--- a/Source_data/hbond_analysis/hbond_result.xlsx
+++ b/Source_data/hbond_analysis/hbond_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Histone_core_cancer_mutation\Source_data\hbond_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCC5068-872E-42F0-8B74-AC751E37D881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BD1D09-DEF9-416A-8C93-B5C899399968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4815" yWindow="5370" windowWidth="28800" windowHeight="15345" xr2:uid="{2BDF9202-92E6-43D7-993B-11D0BA1C76C4}"/>
+    <workbookView xWindow="7290" yWindow="5235" windowWidth="28800" windowHeight="15345" xr2:uid="{2BDF9202-92E6-43D7-993B-11D0BA1C76C4}"/>
   </bookViews>
   <sheets>
     <sheet name="hbond-50" sheetId="1" r:id="rId1"/>
